--- a/SGC-CKN/Excel/2d26a4f3-8876-4ca4-bebc-0089baf28000_Lô_CT-02_P8-1_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/2d26a4f3-8876-4ca4-bebc-0089baf28000_Lô_CT-02_P8-1_D800_23-03-2026.xlsx
@@ -59,7 +59,7 @@
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>16:22 23/03/2026</t>
+    <t>17:27 23/03/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -143,7 +143,7 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">12:50
+    <t xml:space="preserve">13:00
 23/03/2026</t>
   </si>
   <si>
@@ -203,7 +203,7 @@
 23/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">15:30
+    <t xml:space="preserve">15:20
 23/03/2026</t>
   </si>
   <si>
@@ -217,7 +217,7 @@
 23/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:15
+    <t xml:space="preserve">16:05
 23/03/2026</t>
   </si>
   <si>
@@ -227,11 +227,11 @@
     <t>Cuội đa màu sắc TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">16:11
+    <t xml:space="preserve">16:41
 23/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">16:22
+    <t xml:space="preserve">17:27
 23/03/2026</t>
   </si>
   <si>
@@ -272,7 +272,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -355,6 +355,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="12"/>
       <name val="Arial"/>
     </font>
@@ -424,11 +430,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFED7AA"/>
       </patternFill>
     </fill>
@@ -445,6 +446,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF99F6E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC2626"/>
       </patternFill>
     </fill>
     <fill>
@@ -611,52 +617,52 @@
     <xf numFmtId="0" fontId="10" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1315,16 +1321,16 @@
         <v>-8.33</v>
       </c>
       <c r="G13" s="12">
-        <v>-16.18</v>
+        <v>-16.27</v>
       </c>
       <c r="H13" s="12">
         <v>1</v>
       </c>
       <c r="I13" s="12">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="J13" s="8">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="K13" s="13" t="s">
         <v>30</v>
@@ -1347,19 +1353,19 @@
         <v>42</v>
       </c>
       <c r="F14" s="15">
-        <v>-16.18</v>
+        <v>-16.27</v>
       </c>
       <c r="G14" s="15">
         <v>-20.56</v>
       </c>
       <c r="H14" s="15">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="I14" s="15">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="J14" s="8">
-        <v>5.26</v>
+        <v>6.43</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>30</v>
@@ -1385,16 +1391,16 @@
         <v>-20.56</v>
       </c>
       <c r="G15" s="18">
-        <v>-24.13</v>
+        <v>-24.53</v>
       </c>
       <c r="H15" s="18">
         <v>0.32</v>
       </c>
       <c r="I15" s="18">
-        <v>3.57</v>
+        <v>3.97</v>
       </c>
       <c r="J15" s="8">
-        <v>11.27</v>
+        <v>12.54</v>
       </c>
       <c r="K15" s="19" t="s">
         <v>30</v>
@@ -1417,161 +1423,161 @@
         <v>50</v>
       </c>
       <c r="F16" s="21">
-        <v>-24.13</v>
+        <v>-24.53</v>
       </c>
       <c r="G16" s="21">
-        <v>-26.51</v>
+        <v>-34.51</v>
       </c>
       <c r="H16" s="21">
         <v>0.73</v>
       </c>
       <c r="I16" s="21">
-        <v>2.38</v>
-      </c>
-      <c r="J16" s="24">
-        <v>3.25</v>
+        <v>9.98</v>
+      </c>
+      <c r="J16" s="8">
+        <v>13.61</v>
       </c>
       <c r="K16" s="22" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="25">
-        <v>-26.51</v>
-      </c>
-      <c r="G17" s="25">
-        <v>-27.24</v>
-      </c>
-      <c r="H17" s="25">
+      <c r="F17" s="24">
+        <v>-34.51</v>
+      </c>
+      <c r="G17" s="24">
+        <v>-37.24</v>
+      </c>
+      <c r="H17" s="24">
         <v>0.23</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="24">
+        <v>2.73</v>
+      </c>
+      <c r="J17" s="8">
+        <v>11.7</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="29" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="27">
+        <v>-37.24</v>
+      </c>
+      <c r="G18" s="27">
+        <v>-39</v>
+      </c>
+      <c r="H18" s="27">
+        <v>0.32</v>
+      </c>
+      <c r="I18" s="27">
+        <v>1.76</v>
+      </c>
+      <c r="J18" s="8">
+        <v>5.56</v>
+      </c>
+      <c r="K18" s="28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B19" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="F19" s="30">
+        <v>-39</v>
+      </c>
+      <c r="G19" s="30">
+        <v>-44.15</v>
+      </c>
+      <c r="H19" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="I19" s="30">
+        <v>5.15</v>
+      </c>
+      <c r="J19" s="8">
+        <v>20.6</v>
+      </c>
+      <c r="K19" s="31" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="33">
+        <v>-44.15</v>
+      </c>
+      <c r="G20" s="33">
+        <v>-44.88</v>
+      </c>
+      <c r="H20" s="33">
+        <v>0.77</v>
+      </c>
+      <c r="I20" s="33">
         <v>0.73</v>
       </c>
-      <c r="J17" s="24">
-        <v>3.13</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D18" s="30" t="s">
-        <v>57</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="28">
-        <v>-27.24</v>
-      </c>
-      <c r="G18" s="28">
-        <v>-29</v>
-      </c>
-      <c r="H18" s="28">
-        <v>0.48</v>
-      </c>
-      <c r="I18" s="28">
-        <v>1.76</v>
-      </c>
-      <c r="J18" s="24">
-        <v>3.64</v>
-      </c>
-      <c r="K18" s="29" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>62</v>
-      </c>
-      <c r="F19" s="31">
-        <v>-29</v>
-      </c>
-      <c r="G19" s="31">
-        <v>-44.15</v>
-      </c>
-      <c r="H19" s="31">
-        <v>0.42</v>
-      </c>
-      <c r="I19" s="31">
-        <v>15.15</v>
-      </c>
-      <c r="J19" s="8">
-        <v>36.36</v>
-      </c>
-      <c r="K19" s="32" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="34" t="s">
-        <v>63</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="34">
-        <v>-44.15</v>
-      </c>
-      <c r="G20" s="34">
-        <v>-44.88</v>
-      </c>
-      <c r="H20" s="34">
-        <v>0.18</v>
-      </c>
-      <c r="I20" s="34">
-        <v>0.73</v>
-      </c>
-      <c r="J20" s="24">
-        <v>3.98</v>
-      </c>
-      <c r="K20" s="35" t="s">
+      <c r="J20" s="36">
+        <v>0.95</v>
+      </c>
+      <c r="K20" s="34" t="s">
         <v>67</v>
       </c>
     </row>
@@ -1785,16 +1791,16 @@
         <v>-8.33</v>
       </c>
       <c r="F4" s="12">
-        <v>-16.18</v>
+        <v>-16.27</v>
       </c>
       <c r="G4" s="12">
         <v>1</v>
       </c>
       <c r="H4" s="12">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
       <c r="I4" s="8">
-        <v>7.85</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1811,19 +1817,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="15">
-        <v>-16.18</v>
+        <v>-16.27</v>
       </c>
       <c r="F5" s="15">
         <v>-20.56</v>
       </c>
       <c r="G5" s="15">
-        <v>0.83</v>
+        <v>0.67</v>
       </c>
       <c r="H5" s="15">
-        <v>4.38</v>
+        <v>4.29</v>
       </c>
       <c r="I5" s="8">
-        <v>5.26</v>
+        <v>6.43</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1843,16 +1849,16 @@
         <v>-20.56</v>
       </c>
       <c r="F6" s="18">
-        <v>-24.13</v>
+        <v>-24.53</v>
       </c>
       <c r="G6" s="18">
         <v>0.32</v>
       </c>
       <c r="H6" s="18">
-        <v>3.57</v>
+        <v>3.97</v>
       </c>
       <c r="I6" s="8">
-        <v>11.27</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1869,135 +1875,135 @@
         <v>1</v>
       </c>
       <c r="E7" s="21">
-        <v>-24.13</v>
+        <v>-24.53</v>
       </c>
       <c r="F7" s="21">
-        <v>-26.51</v>
+        <v>-34.51</v>
       </c>
       <c r="G7" s="21">
         <v>0.73</v>
       </c>
       <c r="H7" s="21">
-        <v>2.38</v>
-      </c>
-      <c r="I7" s="24">
-        <v>3.25</v>
+        <v>9.98</v>
+      </c>
+      <c r="I7" s="8">
+        <v>13.61</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="25">
+      <c r="A8" s="24">
         <v>7</v>
       </c>
-      <c r="B8" s="25" t="s">
+      <c r="B8" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="24">
         <v>1</v>
       </c>
-      <c r="E8" s="25">
-        <v>-26.51</v>
-      </c>
-      <c r="F8" s="25">
-        <v>-27.24</v>
-      </c>
-      <c r="G8" s="25">
+      <c r="E8" s="24">
+        <v>-34.51</v>
+      </c>
+      <c r="F8" s="24">
+        <v>-37.24</v>
+      </c>
+      <c r="G8" s="24">
         <v>0.23</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="24">
+        <v>2.73</v>
+      </c>
+      <c r="I8" s="8">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="27">
+        <v>8</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="27">
+        <v>1</v>
+      </c>
+      <c r="E9" s="27">
+        <v>-37.24</v>
+      </c>
+      <c r="F9" s="27">
+        <v>-39</v>
+      </c>
+      <c r="G9" s="27">
+        <v>0.32</v>
+      </c>
+      <c r="H9" s="27">
+        <v>1.76</v>
+      </c>
+      <c r="I9" s="8">
+        <v>5.56</v>
+      </c>
+    </row>
+    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
+        <v>9</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="30">
+        <v>1</v>
+      </c>
+      <c r="E10" s="30">
+        <v>-39</v>
+      </c>
+      <c r="F10" s="30">
+        <v>-44.15</v>
+      </c>
+      <c r="G10" s="30">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="30">
+        <v>5.15</v>
+      </c>
+      <c r="I10" s="8">
+        <v>20.6</v>
+      </c>
+    </row>
+    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="33">
+        <v>10</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>64</v>
+      </c>
+      <c r="D11" s="33">
+        <v>1</v>
+      </c>
+      <c r="E11" s="33">
+        <v>-44.15</v>
+      </c>
+      <c r="F11" s="33">
+        <v>-44.88</v>
+      </c>
+      <c r="G11" s="33">
+        <v>0.77</v>
+      </c>
+      <c r="H11" s="33">
         <v>0.73</v>
       </c>
-      <c r="I8" s="24">
-        <v>3.13</v>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="28">
-        <v>8</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="28">
-        <v>1</v>
-      </c>
-      <c r="E9" s="28">
-        <v>-27.24</v>
-      </c>
-      <c r="F9" s="28">
-        <v>-29</v>
-      </c>
-      <c r="G9" s="28">
-        <v>0.48</v>
-      </c>
-      <c r="H9" s="28">
-        <v>1.76</v>
-      </c>
-      <c r="I9" s="24">
-        <v>3.64</v>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="31">
-        <v>9</v>
-      </c>
-      <c r="B10" s="31" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="32" t="s">
-        <v>60</v>
-      </c>
-      <c r="D10" s="31">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31">
-        <v>-29</v>
-      </c>
-      <c r="F10" s="31">
-        <v>-44.15</v>
-      </c>
-      <c r="G10" s="31">
-        <v>0.42</v>
-      </c>
-      <c r="H10" s="31">
-        <v>15.15</v>
-      </c>
-      <c r="I10" s="8">
-        <v>36.36</v>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="34">
-        <v>10</v>
-      </c>
-      <c r="B11" s="34" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34">
-        <v>-44.15</v>
-      </c>
-      <c r="F11" s="34">
-        <v>-44.88</v>
-      </c>
-      <c r="G11" s="34">
-        <v>0.18</v>
-      </c>
-      <c r="H11" s="34">
-        <v>0.73</v>
-      </c>
-      <c r="I11" s="24">
-        <v>3.98</v>
+      <c r="I11" s="36">
+        <v>0.95</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2020,13 +2026,13 @@
         <v>-44.88</v>
       </c>
       <c r="G12" s="39">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="H12" s="39">
         <v>44.88</v>
       </c>
       <c r="I12" s="39">
-        <v>9.29</v>
+        <v>9.13</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/2d26a4f3-8876-4ca4-bebc-0089baf28000_Lô_CT-02_P8-1_D800_23-03-2026.xlsx
+++ b/SGC-CKN/Excel/2d26a4f3-8876-4ca4-bebc-0089baf28000_Lô_CT-02_P8-1_D800_23-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">10:20
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">10:41
@@ -140,7 +140,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">13:00
@@ -154,7 +154,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">13:41
@@ -168,7 +168,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:01
@@ -182,7 +182,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">14:46
@@ -196,7 +196,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1. Cát xám, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">15:01
@@ -210,9 +210,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">15:50
 23/03/2026</t>
   </si>
@@ -224,7 +221,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:41
@@ -1519,13 +1516,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="E19" s="32" t="s">
         <v>61</v>
-      </c>
-      <c r="E19" s="32" t="s">
-        <v>62</v>
       </c>
       <c r="F19" s="30">
         <v>-39</v>
@@ -1548,19 +1545,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="33" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="35" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="35" t="s">
+      <c r="E20" s="35" t="s">
         <v>65</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>66</v>
       </c>
       <c r="F20" s="33">
         <v>-44.15</v>
@@ -1578,12 +1575,12 @@
         <v>0.95</v>
       </c>
       <c r="K20" s="34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1689,31 +1686,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1956,7 +1953,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="31" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D10" s="30">
         <v>1</v>
@@ -1985,7 +1982,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="33">
         <v>1</v>
@@ -2008,7 +2005,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
